--- a/Web/TestCasesWeb/Promociones.xlsx
+++ b/Web/TestCasesWeb/Promociones.xlsx
@@ -1,145 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157E6E7E-7328-47BA-86A7-529A64DB710C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>Num</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Pasos</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Obtained Result</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>PROM001</t>
-  </si>
-  <si>
-    <t>PROM002</t>
-  </si>
-  <si>
-    <t>PROM003</t>
-  </si>
-  <si>
-    <t>PROM004</t>
-  </si>
-  <si>
-    <t>Create promotion</t>
-  </si>
-  <si>
-    <t>Modify promotion</t>
-  </si>
-  <si>
-    <t>Delete promotion</t>
-  </si>
-  <si>
-    <t>1. The promotion is created.</t>
-  </si>
-  <si>
-    <t>1. The user select a restaurant.</t>
-  </si>
-  <si>
-    <t>There is not restaurant.</t>
-  </si>
-  <si>
-    <t>KO</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1-9wAK2QDKQWE1XYiJFvMr1x8IQ1gzbDK/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>pte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 
-</t>
-  </si>
-  <si>
-    <t>Promotions page home</t>
-  </si>
-  <si>
-    <t>1. The promotions page home is correctly.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -168,38 +95,41 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -229,25 +159,13 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
+          <bgColor theme="3" tint="0.5999633777886288"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFF6565"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -535,145 +453,201 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" customWidth="1"/>
-    <col min="5" max="6" width="33.42578125" customWidth="1"/>
-    <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="41.5703125" customWidth="1" min="4" max="4"/>
+    <col width="33.42578125" customWidth="1" min="5" max="6"/>
+    <col width="91.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pasos</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Obtained Result</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="5">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>PROM001</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Promotions page home</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 
+</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1. The promotions page home is correctly.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>pte</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="n"/>
+    </row>
+    <row r="3" customFormat="1" s="5">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>PROM002</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Create promotion</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1. The user select a restaurant.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>1. The promotion is created.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Restaurant selector is now visible in the main header.</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Fixed: added RestaurantSelector to the main page header so it is always visible and allows switching restaurants without needing to hit the empty state first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" customFormat="1" s="5">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>PROM003</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Modify promotion</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>pte</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n"/>
+    </row>
+    <row r="5" customFormat="1" s="5">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>PROM004</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Delete promotion</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>pte</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="G2:G5">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="3" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="2" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="1" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="0" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{88CD9402-5606-4F14-BBE6-177B17338893}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Web/TestCasesWeb/Promociones.xlsx
+++ b/Web/TestCasesWeb/Promociones.xlsx
@@ -1,72 +1,145 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157E6E7E-7328-47BA-86A7-529A64DB710C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Pasos</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Obtained Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>PROM001</t>
+  </si>
+  <si>
+    <t>PROM002</t>
+  </si>
+  <si>
+    <t>PROM003</t>
+  </si>
+  <si>
+    <t>PROM004</t>
+  </si>
+  <si>
+    <t>Create promotion</t>
+  </si>
+  <si>
+    <t>Modify promotion</t>
+  </si>
+  <si>
+    <t>Delete promotion</t>
+  </si>
+  <si>
+    <t>1. The promotion is created.</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant.</t>
+  </si>
+  <si>
+    <t>There is not restaurant.</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-9wAK2QDKQWE1XYiJFvMr1x8IQ1gzbDK/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>pte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 
+</t>
+  </si>
+  <si>
+    <t>Promotions page home</t>
+  </si>
+  <si>
+    <t>1. The promotions page home is correctly.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00276221"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -95,41 +168,38 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -159,13 +229,25 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.5999633777886288"/>
+          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6565"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -453,201 +535,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="41.5703125" customWidth="1" min="4" max="4"/>
-    <col width="33.42578125" customWidth="1" min="5" max="6"/>
-    <col width="91.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" customWidth="1"/>
+    <col min="5" max="6" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Pasos</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Obtained Result</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="5">
-      <c r="A2" s="4" t="n">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>PROM001</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Promotions page home</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. 
-</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>1. The promotions page home is correctly.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>pte</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="n"/>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="7"/>
     </row>
-    <row r="3" customFormat="1" s="5">
-      <c r="A3" s="4" t="n">
+    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>PROM002</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Create promotion</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>1. The user select a restaurant.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>1. The promotion is created.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Restaurant selector is now visible in the main header.</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Fixed: added RestaurantSelector to the main page header so it is always visible and allows switching restaurants without needing to hit the empty state first.</t>
-        </is>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" customFormat="1" s="5">
-      <c r="A4" s="4" t="n">
+    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>PROM003</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Modify promotion</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>pte</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n"/>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="4"/>
     </row>
-    <row r="5" customFormat="1" s="5">
-      <c r="A5" s="4" t="n">
+    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>PROM004</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Delete promotion</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>pte</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n"/>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="G2:G5">
-    <cfRule type="containsText" priority="1" operator="containsText" dxfId="3" text="PTE">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="2" operator="containsText" dxfId="2" text="BL">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="3" operator="containsText" dxfId="1" text="KO">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="4" operator="containsText" dxfId="0" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{88CD9402-5606-4F14-BBE6-177B17338893}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Web/TestCasesWeb/Promociones.xlsx
+++ b/Web/TestCasesWeb/Promociones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157E6E7E-7328-47BA-86A7-529A64DB710C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F18129-2A92-4C0E-9982-06A9C46CB4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="58">
   <si>
     <t>Num</t>
   </si>
@@ -58,9 +58,6 @@
     <t>PROM004</t>
   </si>
   <si>
-    <t>Create promotion</t>
-  </si>
-  <si>
     <t>Modify promotion</t>
   </si>
   <si>
@@ -70,36 +67,173 @@
     <t>1. The promotion is created.</t>
   </si>
   <si>
-    <t>1. The user select a restaurant.</t>
-  </si>
-  <si>
-    <t>There is not restaurant.</t>
-  </si>
-  <si>
     <t>KO</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1-9wAK2QDKQWE1XYiJFvMr1x8IQ1gzbDK/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>pte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 
+    <t>There is not restaurant.
+https://drive.google.com/file/d/1-9wAK2QDKQWE1XYiJFvMr1x8IQ1gzbDK/view?usp=drive_link
+15/04/26: Fixed: added RestaurantSelector to the main page header so it is always visible and allows switching restaurants without needing to hit the empty state first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user sees the promotions page
 </t>
   </si>
   <si>
-    <t>Promotions page home</t>
-  </si>
-  <si>
-    <t>1. The promotions page home is correctly.</t>
+    <t>Promotions page</t>
+  </si>
+  <si>
+    <t>1. The promotions page is correctly.</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>El nombre muy largo de una promoción hace perder la funcionalidad: PROM002.jpg</t>
+  </si>
+  <si>
+    <t>1. The operation is cancelled</t>
+  </si>
+  <si>
+    <t>1. The promotion is modified</t>
+  </si>
+  <si>
+    <t>Modify promotion,cancel</t>
+  </si>
+  <si>
+    <t>The promotion is deleted</t>
+  </si>
+  <si>
+    <t>Delete promotion,cancel</t>
+  </si>
+  <si>
+    <t>PROM005</t>
+  </si>
+  <si>
+    <t>PROM006</t>
+  </si>
+  <si>
+    <t>PROM007</t>
+  </si>
+  <si>
+    <t>PROM008</t>
+  </si>
+  <si>
+    <t>Change restaurant</t>
+  </si>
+  <si>
+    <t>1. The user changes the restaurant
+2. He cans create,modify and delete promotions in another restaurant</t>
+  </si>
+  <si>
+    <t>Create a new promotion, all parameters</t>
+  </si>
+  <si>
+    <t>Create a first promotion, all parameters</t>
+  </si>
+  <si>
+    <t>Create a first promotion, cancel</t>
+  </si>
+  <si>
+    <t>Create a new promotion, mandatory parameters</t>
+  </si>
+  <si>
+    <t>Create a first promotion, mandatory parameters</t>
+  </si>
+  <si>
+    <t>Createa a new promotions, cancel</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Clicks "Nueva promoción"
+3. Fills de mandatory fields
+4. Clicks "Crear promoción"</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Fills de mandatory  fields
+3. Clicks "Crear promoción"</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Clicks "Crear primera promoción"
+3. Fills de all fields
+3. Clicks "Crear promoción"</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Clicks "Nueva promoción"
+3. Fills de all fields
+4. Clicks "Crear promoción"</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Clicks "Nueva promoción"
+2. Fills de all fields
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Selects the promotion, clicks the pencil
+3. Modify field
+4. Clicks "Guardar"</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Selects the promotion, clicks the garvage
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Selects the promotion, clicks the garvage
+3. Clicks "Guardar"</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Selects the promotion, clicks the pencil
+3. Modify field
+4. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Clicks "Crear primera promoción"
+3. Fills de all fields
+4. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user changes the restaurant and create,modify and delete promotions </t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Selects a promotion
+3. Changes the status</t>
+  </si>
+  <si>
+    <t>1. The status is changed</t>
+  </si>
+  <si>
+    <t>Activate/deactivate promotion</t>
+  </si>
+  <si>
+    <t>PROM009</t>
+  </si>
+  <si>
+    <t>PROM010</t>
+  </si>
+  <si>
+    <t>PROM011</t>
+  </si>
+  <si>
+    <t>PROM012</t>
+  </si>
+  <si>
+    <t>PROM013</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,14 +252,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -166,11 +292,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -187,18 +312,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -536,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -580,21 +698,23 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -602,25 +722,25 @@
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -628,17 +748,23 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -646,19 +772,241 @@
         <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4"/>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G5">
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
@@ -673,7 +1021,7 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{88CD9402-5606-4F14-BBE6-177B17338893}"/>
+    <hyperlink ref="H3" r:id="rId1" display="https://drive.google.com/file/d/1-9wAK2QDKQWE1XYiJFvMr1x8IQ1gzbDK/view?usp=drive_link_x000a_15/04/26: Fixed: added RestaurantSelector to the main page header so it is always visible and allows switching restaurants without needing to hit the empty state first." xr:uid="{88CD9402-5606-4F14-BBE6-177B17338893}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Web/TestCasesWeb/Promociones.xlsx
+++ b/Web/TestCasesWeb/Promociones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F18129-2A92-4C0E-9982-06A9C46CB4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B05A54-2B18-4CC9-A9C1-A85FBE25ABED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
   <si>
     <t>Num</t>
   </si>
@@ -58,21 +58,10 @@
     <t>PROM004</t>
   </si>
   <si>
-    <t>Modify promotion</t>
-  </si>
-  <si>
-    <t>Delete promotion</t>
-  </si>
-  <si>
     <t>1. The promotion is created.</t>
   </si>
   <si>
     <t>KO</t>
-  </si>
-  <si>
-    <t>There is not restaurant.
-https://drive.google.com/file/d/1-9wAK2QDKQWE1XYiJFvMr1x8IQ1gzbDK/view?usp=drive_link
-15/04/26: Fixed: added RestaurantSelector to the main page header so it is always visible and allows switching restaurants without needing to hit the empty state first.</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user sees the promotions page
@@ -97,15 +86,9 @@
     <t>1. The promotion is modified</t>
   </si>
   <si>
-    <t>Modify promotion,cancel</t>
-  </si>
-  <si>
     <t>The promotion is deleted</t>
   </si>
   <si>
-    <t>Delete promotion,cancel</t>
-  </si>
-  <si>
     <t>PROM005</t>
   </si>
   <si>
@@ -116,31 +99,13 @@
   </si>
   <si>
     <t>PROM008</t>
-  </si>
-  <si>
-    <t>Change restaurant</t>
   </si>
   <si>
     <t>1. The user changes the restaurant
 2. He cans create,modify and delete promotions in another restaurant</t>
   </si>
   <si>
-    <t>Create a new promotion, all parameters</t>
-  </si>
-  <si>
-    <t>Create a first promotion, all parameters</t>
-  </si>
-  <si>
-    <t>Create a first promotion, cancel</t>
-  </si>
-  <si>
     <t>Create a new promotion, mandatory parameters</t>
-  </si>
-  <si>
-    <t>Create a first promotion, mandatory parameters</t>
-  </si>
-  <si>
-    <t>Createa a new promotions, cancel</t>
   </si>
   <si>
     <t>1. The user select a restaurant
@@ -203,37 +168,140 @@
     <t xml:space="preserve">1. The user changes the restaurant and create,modify and delete promotions </t>
   </si>
   <si>
+    <t>PROM009</t>
+  </si>
+  <si>
+    <t>PROM010</t>
+  </si>
+  <si>
+    <t>PROM011</t>
+  </si>
+  <si>
+    <t>PROM012</t>
+  </si>
+  <si>
+    <t>PROM013</t>
+  </si>
+  <si>
+    <t>Promotions: Create a first promotion, mandatory parameters</t>
+  </si>
+  <si>
+    <t>Promotions: Create a first promotion, all parameters</t>
+  </si>
+  <si>
+    <t>Promotions: Create a first promotion, cancel</t>
+  </si>
+  <si>
+    <t>Promotions: Create a new promotion, all parameters</t>
+  </si>
+  <si>
+    <t>Promotions: Createa a new promotions, cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promotions: Modify </t>
+  </si>
+  <si>
+    <t>Promotions: Modify, cancel</t>
+  </si>
+  <si>
+    <t>Promotions: Delete</t>
+  </si>
+  <si>
+    <t>Promotions: Delete,cancel</t>
+  </si>
+  <si>
+    <t>Promotions: Change restaurant</t>
+  </si>
+  <si>
+    <t>Promotions: Activate</t>
+  </si>
+  <si>
+    <t>Promotions: Deactivate</t>
+  </si>
+  <si>
     <t>1. The user select a restaurant
 2. Selects a promotion
-3. Changes the status</t>
-  </si>
-  <si>
-    <t>1. The status is changed</t>
-  </si>
-  <si>
-    <t>Activate/deactivate promotion</t>
-  </si>
-  <si>
-    <t>PROM009</t>
-  </si>
-  <si>
-    <t>PROM010</t>
-  </si>
-  <si>
-    <t>PROM011</t>
-  </si>
-  <si>
-    <t>PROM012</t>
-  </si>
-  <si>
-    <t>PROM013</t>
+3. Activate promotion</t>
+  </si>
+  <si>
+    <t>1. The user select a restaurant
+2. Selects a promotion
+3. Deactivate promotion</t>
+  </si>
+  <si>
+    <t>1. The promotion is activated</t>
+  </si>
+  <si>
+    <t>1. The promotion is deactivated</t>
+  </si>
+  <si>
+    <t>PROM014</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is not restaurant:promo002.jpg
+15/04/26: Fixed: added RestaurantSelector to the main page header so it is always visible and allows switching restaurants without needing to hit the empty state first.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No hay control de horas, que fecha fin, sea mayor que fecha inicio: PROMO001.jpg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Se ven muy mal las categorías: PROMO003.jpg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mensaje de error incorrecto si los nombres/descripciones son muy largos: PROMO004.jpg</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,6 +323,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -654,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -698,23 +773,23 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -722,22 +797,20 @@
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -748,19 +821,19 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H4" s="3"/>
     </row>
@@ -772,19 +845,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H5" s="3"/>
     </row>
@@ -793,22 +866,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H6" s="3"/>
     </row>
@@ -817,22 +890,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H7" s="3"/>
     </row>
@@ -841,22 +914,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H8" s="3"/>
     </row>
@@ -865,22 +938,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -889,22 +962,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H10" s="4"/>
     </row>
@@ -913,22 +986,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H11" s="4"/>
     </row>
@@ -937,22 +1010,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H12" s="4"/>
     </row>
@@ -961,22 +1034,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H13" s="4"/>
     </row>
@@ -985,28 +1058,52 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="4"/>
+      <c r="E15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G15">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
@@ -1020,9 +1117,6 @@
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" display="https://drive.google.com/file/d/1-9wAK2QDKQWE1XYiJFvMr1x8IQ1gzbDK/view?usp=drive_link_x000a_15/04/26: Fixed: added RestaurantSelector to the main page header so it is always visible and allows switching restaurants without needing to hit the empty state first." xr:uid="{88CD9402-5606-4F14-BBE6-177B17338893}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Web/TestCasesWeb/Promociones.xlsx
+++ b/Web/TestCasesWeb/Promociones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B05A54-2B18-4CC9-A9C1-A85FBE25ABED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB9B8CA-6BF4-41A2-90E2-0D32F1ACB761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2445" yWindow="0" windowWidth="23265" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,50 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Mensaje de error incorrecto si los nombres/descripciones son muy largos: PROMO004.jpg</t>
+      <t>Mensaje de error incorrecto si los nombres/descripciones son muy largos: PROMO004.jpg
+Se pulsa el boton para eliminar, pero no se puede xq el texto no muestra los botones para seguir:PROMO005.jpg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>El mensaje de error se queda abajo, fijo:PROMO006.jpg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La secuencia de días empieza en D en vez de en L: PROMO007.jpg</t>
     </r>
   </si>
 </sst>
@@ -789,7 +832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
